--- a/returns_tasks.xlsx
+++ b/returns_tasks.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-31T01:50:03</t>
+          <t>2026-07-31T13:31:26</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-31T01:50:07</t>
+          <t>2026-07-31T13:31:28</t>
         </is>
       </c>
     </row>
